--- a/astro-site/public/dl/guia-chocolateria-obrador/plan-financiero-3-anos-chocolateria.xlsx
+++ b/astro-site/public/dl/guia-chocolateria-obrador/plan-financiero-3-anos-chocolateria.xlsx
@@ -31,7 +31,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Escenarios'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Escenarios'!$A$1:$E$25</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Personal'!$5:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Personal'!$A$1:$L$47</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Personal'!$A$1:$L$46</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Tesorería 12 meses'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Tesorería 12 meses'!$A$1:$O$50</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Financiación'!$25:$25</definedName>
@@ -434,40 +434,40 @@
     </comment>
     <comment ref="E13" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Revisión salarial 2026 del convenio 28001025011981 · BOCM núm. 50, de 28-02-2026 (BOCM-20260228-2) · https://www.bocm.es/boletin/CM_Orden_BOCM/2026/02/28/BOCM-20260228-2.PDF · TABLA DE EJEMPLO: convenio 28001025011981, «CONFITERIAS PASTELERIAS Y REPOSTERIA (COMERCIO E INDUSTRIA)» (Madrid), vigencia 01/01/2024 a 31/12/2026, tablas de 2026 a 15 pagas. CADUCAN el 31-12-2026.</t>
+        <t>Verificado el 12-09-2026 · Revisión salarial 2026 del convenio 28001025011981 · BOCM núm. 50, de 28-02-2026 (BOCM-20260228-2) · https://www.bocm.es/boletin/CM_Orden_BOCM/2026/02/28/BOCM-20260228-2.PDF · TABLA DE EJEMPLO: convenio 28001025011981, «CONFITERÍAS PASTELERÍAS Y REPOSTERÍA (COMERCIO E INDUSTRIA)» (Madrid), vigencia 01/01/2024 a 31/12/2026, tablas de 2026 a 15 pagas. CADUCAN el 31-12-2026.</t>
       </text>
     </comment>
-    <comment ref="B22" authorId="0" shapeId="0">
+    <comment ref="B21" authorId="0" shapeId="0">
       <text>
         <t>Verificado el 12-09-2026 · Real Decreto 126/2026, de 18 de febrero (BOE-A-2026-3815), arts. 1, 3.1 y 4.1 · https://www.boe.es/buscar/act.php?id=BOE-A-2026-3815</t>
       </text>
     </comment>
-    <comment ref="B27" authorId="0" shapeId="0">
+    <comment ref="B26" authorId="0" shapeId="0">
       <text>
         <t>Salarios de mercado — Chocolatero / bombonero especializado (CHS-69a) · Fuente: Insertia · Consultada el 2026-09-12 · https://www.insertia.net/blog/cuanto-cobra-un-pastelero-en-espana-sueldo-por-hora-dia-y-mes-segun-convenio-de-pasteleria</t>
       </text>
     </comment>
-    <comment ref="B28" authorId="0" shapeId="0">
+    <comment ref="B27" authorId="0" shapeId="0">
       <text>
         <t>Salarios de mercado — Oficial de primera (CHS-69b) · Fuente: Insertia · Consultada el 2026-09-12 · https://www.insertia.net/blog/cuanto-cobra-un-pastelero-en-espana-sueldo-por-hora-dia-y-mes-segun-convenio-de-pasteleria</t>
       </text>
     </comment>
-    <comment ref="B29" authorId="0" shapeId="0">
+    <comment ref="B28" authorId="0" shapeId="0">
       <text>
         <t>Salarios de mercado — Auxiliar / ayudante (CHS-69c) · Fuente: Insertia · Consultada el 2026-09-12 · https://www.insertia.net/blog/cuanto-cobra-un-pastelero-en-espana-sueldo-por-hora-dia-y-mes-segun-convenio-de-pasteleria</t>
       </text>
     </comment>
-    <comment ref="B30" authorId="0" shapeId="0">
+    <comment ref="B29" authorId="0" shapeId="0">
       <text>
         <t>Salarios de mercado — Encargado / maestro (CHS-69d) · Fuente: Insertia · Consultada el 2026-09-12 · https://www.insertia.net/blog/cuanto-cobra-un-pastelero-en-espana-sueldo-por-hora-dia-y-mes-segun-convenio-de-pasteleria</t>
       </text>
     </comment>
-    <comment ref="A34" authorId="0" shapeId="0">
+    <comment ref="A33" authorId="0" shapeId="0">
       <text>
         <t>Verificado el 12-09-2026 · Registro y Depósito de Convenios Colectivos, Acuerdos Colectivos de Trabajo y Planes de Igualdad (REGCON), Ministerio de Trabajo y Economía Social · consulta pública · https://expinterweb.mites.gob.es/regcon/pub/consultaPublica</t>
       </text>
     </comment>
-    <comment ref="B34" authorId="0" shapeId="0">
+    <comment ref="B33" authorId="0" shapeId="0">
       <text>
         <t>Verificado el 12-09-2026 · Registro y Depósito de Convenios Colectivos, Acuerdos Colectivos de Trabajo y Planes de Igualdad (REGCON), Ministerio de Trabajo y Economía Social · consulta pública · https://expinterweb.mites.gob.es/regcon/pub/consultaPublica</t>
       </text>
@@ -1397,14 +1397,14 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>Cobro al contado y dentro de la nota del 644.5 sin discusion: vendes en las propias dependencias. Es el canal que paga el alquiler.</t>
+          <t>Cobro al contado y dentro de la nota del 644.5 sin discusión: vendes en las propias dependencias. Es el canal que paga el alquiler.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="62" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>Online con envio refrigerado</t>
+          <t>Online con envío refrigerado</t>
         </is>
       </c>
       <c r="B7" s="16" t="n">
@@ -1444,14 +1444,14 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>LO QUE SI ESTA VERIFICADO: vender online al consumidor SIGUE SIENDO comercio al por menor a efectos del IAE, porque la Regla 4.a.2.D) lo define por el destino y comprende el realizado sin establecimiento (`CHN-95`); y vender por internet NO cambia tu registro sanitario (`CHN-90`). LO QUE NO ESTA VERIFICADO es si la condicion de la nota del 644.5 sobre la FABRICACION se rompe al comercializar fuera de las dependencias: eso es lo que hay que preguntar al asesor. Lo que si cambia: te conviertes en ENVASADOR (`CHN-59`) y respondes de la temperatura en el camion (`CHN-88`), mas la informacion obligatoria ANTES de pagar (`CHN-57`). Coste de envio refrigerado de 8,50 euros: SUPUESTO, y es el numero que decide si el canal existe. PARADO de junio a septiembre (`VALLE`).</t>
+          <t>LO QUE SI ESTA VERIFICADO: vender online al consumidor SIGUE SIENDO comercio al por menor a efectos del IAE, porque la Regla 4.a.2.D) lo define por el destino y comprende el realizado sin establecimiento (`CHN-95`); y vender por internet NO cambia tu registro sanitario (`CHN-90`). LO QUE NO ESTA VERIFICADO es si la condición de la nota del 644.5 sobre la FABRICACION se rompe al comercializar fuera de las dependencias: eso es lo que hay que preguntar al asesor. Lo que si cambia: te conviertes en ENVASADOR (`CHN-59`) y respondes de la temperatura en el camión (`CHN-88`), mas la información obligatoria ANTES de pagar (`CHN-57`). Coste de envío refrigerado de 8,50 euros: SUPUESTO, y es el número que decide si el canal existe. PARADO de junio a septiembre (`VALLE`).</t>
         </is>
       </c>
     </row>
     <row r="8" ht="62" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>B2B a hosteleria</t>
+          <t>B2B a hostelería</t>
         </is>
       </c>
       <c r="B8" s="16" t="n">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>Peor margen y cobro a 45 dias: financias tu. Y es el canal que puede meterte en el art. 3 del RD 1021/2022 si dejas de ser marginal, localizado o restringido - los TRES requisitos son ACUMULATIVOS, y basta con servir a UN SOLO cliente inscrito en el RGSEAA para perder «restringido» (`CHN-41`). «Marginal» tiene DOS vias independientes: hasta el 25 % del volumen anual O hasta 500 kg/semana. Y los 500 kg NO incluyen el mostrador: el art. 3 solo habla del suministro a otros minoristas de distinta titularidad.</t>
+          <t>Peor margen y cobro a 45 días: financias tu. Y es el canal que puede meterte en el art. 3 del RD 1021/2022 si dejas de ser marginal, localizado o restringido - los TRES requisitos son ACUMULATIVOS, y basta con servir a UN SOLO cliente inscrito en el RGSEAA para perder «restringido» (`CHN-41`). «Marginal» tiene DOS vías independientes: hasta el 25 % del volumen anual O hasta 500 kg/semana. Y los 500 kg NO incluyen el mostrador: el art. 3 solo habla del suministro a otros minoristas de distinta titularidad.</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>PLAZO MINIMO VERIFICADO: 14 dias desde la aprobacion de la muestra, con minimos de fabricacion de 10 a 25 cajas (`CHS-55`). Es lo que decide si aceptas un pedido de empresa el 15 de diciembre. Y es el canal que obliga a la SEGUNDA TABLA del libro 9: el art. 5.3.b) del EUDR exige registrar a quien suministras, y conservarlo cinco anos (`CHN-24`, D48). El pedido minimo (250 euros) y los 30 dias de cobro son supuestos.</t>
+          <t>PLAZO MÍNIMO VERIFICADO: 14 días desde la aprobación de la muestra, con mínimos de fabricación de 10 a 25 cajas (`CHS-55`). Es lo que decide si aceptas un pedido de empresa el 15 de diciembre. Y es el canal que obliga a la SEGUNDA TABLA del libro 9: el art. 5.3.b) del EUDR exige registrar a quien suministras, y conservarlo cinco años (`CHN-24`, D48). El pedido mínimo (250 euros) y los 30 días de cobro son supuestos.</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>25-45 euros/persona, minimo habitual de 6 personas y 90-150 minutos (`CHS-30`). El aforo de 12 y las 3 horas de docente (preparacion y recogida incluidas) son SUPUESTOS. LA UNICA LINEA QUE FUNCIONA EN AGOSTO y que no depende del precio del cacao: por eso su hoja calcula euros/hora de sala dando taller frente a euros/hora de la misma sala vendiendo. IVA: NO esta exento (el art. 20.Uno.10.o excluye las clases para cuya realizacion haya que darse de alta en las tarifas empresariales del IAE, `CHN-71b`), pero el TIPO NO SE CIERRA y la guia NO publica ninguna cifra de tipo (D42e). Y ojo con la columna del 644.5: el taller NO comercializa bombones fuera de tus dependencias, asi que no rompe la nota del epigrafe. Lo que si abre es otra pregunta, y es la del propio `CHN-71b`: si la Hacienda entiende que hay que darse de alta por esta actividad, eso es un alta distinta, no un problema de la nota del 644.5. Los TRES canales que la rompen son el online, el B2B y el corporativo.</t>
+          <t>25-45 euros/persona, mínimo habitual de 6 personas y 90-150 minutos (`CHS-30`). El aforo de 12 y las 3 horas de docente (preparación y recogida incluidas) son SUPUESTOS. LA ÚNICA LÍNEA QUE FUNCIONA EN AGOSTO y que no depende del precio del cacao: por eso su hoja calcula euros/hora de sala dando taller frente a euros/hora de la misma sala vendiendo. IVA: NO esta exento (el art. 20.Uno.10.o excluye las clases para cuya realización haya que darse de alta en las tarifas empresariales del IAE, `CHN-71b`), pero el TIPO NO SE CIERRA y la guía NO publica ninguna cifra de tipo (D42e). Y ojo con la columna del 644.5: el taller NO comercializa bombones fuera de tus dependencias, así que no rompe la nota del epígrafe. Lo que si abre es otra pregunta, y es la del propio `CHN-71b`: si la Hacienda entiende que hay que darse de alta por esta actividad, eso es un alta distinta, no un problema de la nota del 644.5. Los TRES canales que la rompen son el online, el B2B y el corporativo.</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Mi epigrafe es el 644.5, cuya nota permite fabricar bombones «siempre que su comercializacion se realice en las propias dependencias de venta». Voy a vender ademas por este canal: [CANAL]. Con la Regla 4.a.1 del RDLeg 1175/1990 delante -una cuota faculta exclusivamente para su actividad-, ¿ese canal me obliga a dar otra alta, y cual? Y si la respuesta es el epigrafe industrial 421.1, ¿que consecuencias tiene que el Anexo de la Ley 12/2012 liste el 644.5 y no el 421.1?</t>
+          <t>Mi epígrafe es el 644.5, cuya nota permite fabricar bombones «siempre que su comercialización se realice en las propias dependencias de venta». Voy a vender además por este canal: [CANAL]. Con la Regla 4.a.1 del RDLeg 1175/1990 delante -una cuota faculta exclusivamente para su actividad-, ¿ese canal me obliga a dar otra alta, y cual? Y si la respuesta es el epígrafe industrial 421.1, ¿que consecuencias tiene que el Anexo de la Ley 12/2012 liste el 644.5 y no el 421.1?</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="B14" s="14">
-        <f>IFERROR('Personal'!$B$45,"")</f>
+        <f>IFERROR('Personal'!$B$44,"")</f>
         <v>18.49165895571712</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>SUPUESTO: 6 días por semana x 52 semanas = 312, menos 8 días de cierre por festivos. En AGOSTO NO SE CIERRA: lo que para es el obrador, no la tienda, y el literal del kit lo dice («la tienda abre para el turista aunque el obrador pare»). Una bombonería de menos de 300 m2 tiene libertad horaria por el art. 5.2 de la Ley de Horarios Comerciales, no por el 5.1.</t>
+          <t>SUPUESTO: 6 días por semana x 52 semanas = 312, menos 8 días de cierre por festivos. En AGOSTO NO SE CIERRA: lo que para es el obrador, no la tienda, y el literal del kit lo dice («la tienda abre para el turista aunque el obrador pare»). Una bombonería de menos de 300 m² tiene libertad horaria por el art. 5.2 de la Ley de Horarios Comerciales, no por el 5.1.</t>
         </is>
       </c>
     </row>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>SUPUESTO para una ciudad media. La renta observada en los ocho traspasos verificados va de 910 €/mes (74 m2 en Madrid-Vallecas) a 2.200 €/mes (180 m2 en Barcelona); aquí se toma la parte baja porque ninguna de esas dos ciudades es una ciudad media.</t>
+          <t>SUPUESTO para una ciudad media. La renta observada en los ocho traspasos verificados va de 910 €/mes (74 m² en Madrid-Vallecas) a 2.200 €/mes (180 m² en Barcelona); aquí se toma la parte baja porque ninguna de esas dos ciudades es una ciudad media.</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Gestoria y asesoria</t>
+          <t>Gestoría y asesoría</t>
         </is>
       </c>
       <c r="B22" s="13" t="n">
@@ -4890,7 +4890,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Telefonia e internet</t>
+          <t>Telefonía e internet</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>SUPUESTO: mantenimiento de freidora y extracción, y la inspección periódica de la instalación de gas cada cinco años, repercutida. Y una que no es un euro pero cuesta tiempo: la bombonería se libra de la licencia previa de actividad hasta 750 m2 y la chocolatería de taza NO, porque su grupo de IAE no está en el Anexo de esa ley.</t>
+          <t>SUPUESTO: mantenimiento de freidora y extracción, y la inspección periódica de la instalación de gas cada cinco años, repercutida. Y una que no es un euro pero cuesta tiempo: la bombonería se libra de la licencia previa de actividad hasta 750 m² y la chocolatería de taza NO, porque su grupo de IAE no está en el Anexo de esa ley.</t>
         </is>
       </c>
     </row>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>Son DOS NEGOCIOS, y la norma los separa sola: el Anexo de la Ley 12/2012 incluye el epígrafe 644.5 de bombones y caramelos y no contiene ningún grupo de la agrupación 67, donde está la chocolatería de taza. Antes de mirar el margen, mira eso: la bombonería se libra de la licencia previa de actividad hasta 750 m2 y la taza no.</t>
+          <t>Son DOS NEGOCIOS, y la norma los separa sola: el Anexo de la Ley 12/2012 incluye el epígrafe 644.5 de bombones y caramelos y no contiene ningún grupo de la agrupación 67, donde está la chocolatería de taza. Antes de mirar el margen, mira eso: la bombonería se libra de la licencia previa de actividad hasta 750 m² y la taza no.</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -7422,7 +7422,7 @@
         </is>
       </c>
       <c r="E6" s="14">
-        <f>IFERROR(INDEX($E$13:$E$18,MATCH(D6,$A$13:$A$18,0)),"")</f>
+        <f>IFERROR(INDEX($E$13:$E$17,MATCH(D6,$A$13:$A$17,0)),"")</f>
         <v>1427.89</v>
       </c>
       <c r="F6" s="14">
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="E7" s="14">
-        <f>IFERROR(INDEX($E$13:$E$18,MATCH(D7,$A$13:$A$18,0)),"")</f>
+        <f>IFERROR(INDEX($E$13:$E$17,MATCH(D7,$A$13:$A$17,0)),"")</f>
         <v>1376.91</v>
       </c>
       <c r="F7" s="14">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>Turno de Manana (07:00-15:00).</t>
+          <t>Turno de Mañana (07:00-15:00).</t>
         </is>
       </c>
     </row>
@@ -7524,7 +7524,7 @@
         </is>
       </c>
       <c r="E8" s="14">
-        <f>IFERROR(INDEX($E$13:$E$18,MATCH(D8,$A$13:$A$18,0)),"")</f>
+        <f>IFERROR(INDEX($E$13:$E$17,MATCH(D8,$A$13:$A$17,0)),"")</f>
         <v>1249.42</v>
       </c>
       <c r="F8" s="14">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Tecnicos y titulados superiores</t>
+          <t>Técnicos y titulados superiores</t>
         </is>
       </c>
       <c r="E13" s="13" t="n">
@@ -7677,7 +7677,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Direccion, jefes y encargados</t>
+          <t>Dirección, jefes y encargados</t>
         </is>
       </c>
       <c r="E14" s="13" t="n">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>especialista de produccion, encargado de seccion</t>
+          <t>especialista de producción, encargado de sección</t>
         </is>
       </c>
     </row>
@@ -7752,7 +7752,7 @@
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>personal cualificado de produccion y de envasado, dependiente</t>
+          <t>personal cualificado de producción y de envasado, dependiente</t>
         </is>
       </c>
     </row>
@@ -7764,7 +7764,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Personal de apoyo</t>
+          <t>Personal de apoyo y ayuda en servicios auxiliares</t>
         </is>
       </c>
       <c r="E17" s="13" t="n">
@@ -7781,416 +7781,387 @@
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>ayudante de produccion, ayudante de comercio</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Grupo 6</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Personal de ayuda en servicios auxiliares</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="n">
-        <v>1192.42</v>
-      </c>
-      <c r="F18" s="14">
-        <f>IFERROR(E18*MAX(12,'0. Supuestos'!$B$30),"")</f>
+          <t>ayudante de producción, ayudante de comercio, peón, limpiador, almacenero</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>CONTRASTE CON EL SMI</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Bruto anual del grupo más bajo (€)</t>
+        </is>
+      </c>
+      <c r="B20" s="14">
+        <f>IFERROR(IF(COUNT(F13:F17)=0,"",MIN(F13:F17)),"")</f>
         <v>17886.300000000003</v>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>OBRADOR / TIENDA</t>
-        </is>
-      </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>peon, limpiador, almacenero</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>CONTRASTE CON EL SMI</t>
-        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bruto anual del grupo más bajo (€)</t>
+          <t>SMI anual de referencia (€)</t>
         </is>
       </c>
       <c r="B21" s="14">
-        <f>IFERROR(IF(COUNT(F13:F18)=0,"",MIN(F13:F18)),"")</f>
-        <v>17886.300000000003</v>
+        <f>IFERROR('0. Supuestos'!$B$31,"")</f>
+        <v>17094.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SMI anual de referencia (€)</t>
-        </is>
-      </c>
-      <c r="B22" s="14">
-        <f>IFERROR('0. Supuestos'!$B$31,"")</f>
-        <v>17094.0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
           <t>¿Algún grupo queda por debajo del SMI?</t>
         </is>
       </c>
-      <c r="B23" t="str">
-        <f>IFERROR(IF(B21="","",IF(B21&lt;B22,"Sí: revísalo con tu asesor","No: aquí manda el convenio")),"")</f>
+      <c r="B22" t="str">
+        <f>IFERROR(IF(B20="","",IF(B20&lt;B21,"Sí: revísalo con tu asesor","No: aquí manda el convenio")),"")</f>
         <v>No: aquí manda el convenio</v>
       </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="L22" s="5" t="inlineStr">
         <is>
           <t>El SMI es una referencia ANUAL en cómputo global, no un mínimo por concepto. En este sector manda el convenio: el grupo más bajo de la tabla de ejemplo ya lo supera. Las dos cosas caducan el 31-12-2026.</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>SALARIOS DE MERCADO (orientativos, y NUNCA un convenio)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>Etiqueta de la fuente salarial</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>Mín. (€/h)</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>Máx. (€/h)</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>Equivale a</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>Coste año a jornada completa (€)</t>
         </is>
       </c>
-      <c r="L26" s="7" t="inlineStr">
+      <c r="L25" s="7" t="inlineStr">
         <is>
           <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>«Chocolatero / bombonero especializado»</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="C26" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Chocolatero</t>
+        </is>
+      </c>
+      <c r="E26" s="14">
+        <f>IFERROR(B26*$B$42*(1+'0. Supuestos'!$B$29),"")</f>
+        <v>30776.2</v>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>Fiabilidad media, y NUNCA se presentan como tabla de convenio. Las etiquetas entrecomilladas son las de la FUENTE salarial, no los perfiles de esta casa: los perfiles son los tres del kit, y la columna «Equivale a» está para eso. Sirven para saber si lo que vas a ofrecer está dentro de mercado; lo que te OBLIGA es tu convenio.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>«Chocolatero / bombonero especializado»</t>
+          <t>«Oficial de primera»</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C27" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="C27" s="13" t="n">
-        <v>16</v>
-      </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>Chocolatero</t>
         </is>
       </c>
       <c r="E27" s="14">
-        <f>IFERROR(B27*$B$43*(1+'0. Supuestos'!$B$29),"")</f>
-        <v>30776.2</v>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>Fiabilidad media, y NUNCA se presentan como tabla de convenio. Las etiquetas entrecomilladas son las de la FUENTE salarial, no los perfiles de esta casa: los perfiles son los tres del kit, y la columna «Equivale a» está para eso. Sirven para saber si lo que vas a ofrecer está dentro de mercado; lo que te OBLIGA es tu convenio.</t>
-        </is>
+        <f>IFERROR(B27*$B$42*(1+'0. Supuestos'!$B$29),"")</f>
+        <v>26041.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>«Oficial de primera»</t>
+          <t>«Auxiliar / ayudante»</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>13</v>
+        <v>9.5</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Chocolatero</t>
+          <t>Dependiente</t>
         </is>
       </c>
       <c r="E28" s="14">
-        <f>IFERROR(B28*$B$43*(1+'0. Supuestos'!$B$29),"")</f>
-        <v>26041.4</v>
+        <f>IFERROR(B28*$B$42*(1+'0. Supuestos'!$B$29),"")</f>
+        <v>18939.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>«Auxiliar / ayudante»</t>
+          <t>«Encargado / maestro»</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>9.5</v>
+        <v>20</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Dependiente</t>
+          <t>Encargado</t>
         </is>
       </c>
       <c r="E29" s="14">
-        <f>IFERROR(B29*$B$43*(1+'0. Supuestos'!$B$29),"")</f>
-        <v>18939.2</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>«Encargado / maestro»</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C30" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Encargado</t>
-        </is>
-      </c>
-      <c r="E30" s="14">
-        <f>IFERROR(B30*$B$43*(1+'0. Supuestos'!$B$29),"")</f>
+        <f>IFERROR(B29*$B$42*(1+'0. Supuestos'!$B$29),"")</f>
         <v>35511.0</v>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>LOS CUATRO CONVENIOS DE ÁMBITO PROVINCIAL O SUPERIOR QUE SÍ NOMBRAN CHOCOLATES O BOMBONES</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Ámbito</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>Denominación</t>
         </is>
       </c>
-      <c r="L33" s="7" t="inlineStr">
+      <c r="L32" s="7" t="inlineStr">
         <is>
           <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>45000145011981</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>ESTÁ PROBADO que NO existe convenio ESTATAL del chocolate: el registro oficial devuelve «no se ha encontrado ningún acuerdo» para chocolate, bombones, confitería y pastelería, y el control con «turrones» devuelve 29 trámites, así que la consulta funciona. Estos cuatro existen y nombran el producto, pero su ámbito FUNCIONAL es una pregunta para un laboralista, no una respuesta de esta guía.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>45000145011981</t>
+          <t>80000725012008</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Toledo</t>
+          <t>Comunitat Valenciana</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L34" s="5" t="inlineStr">
-        <is>
-          <t>ESTÁ PROBADO que NO existe convenio ESTATAL del chocolate: el registro oficial devuelve «no se ha encontrado ningún acuerdo» para chocolate, bombones, confitería y pastelería, y el control con «turrones» devuelve 29 trámites, así que la consulta funciona. Estos cuatro existen y nombran el producto, pero su ámbito FUNCIONAL es una pregunta para un laboralista, no una respuesta de esta guía.</t>
+          <t>CHOCOLATES, TORREFACTORES DE CAFES Y SUCEDANEOS (01/01/2023-31/12/2026)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>80000725012008</t>
+          <t>01000425011981</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Comunitat Valenciana</t>
+          <t>Alava</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>CHOCOLATES, TORREFACTORES DE CAFES Y SUCEDANEOS (01/01/2023-31/12/2026)</t>
+          <t>caducado</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>01000425011981</t>
+          <t>22001125012010</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Alava</t>
+          <t>Huesca</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>caducado</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>22001125012010</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Huesca</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="38"/>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>HORAS, DIMENSIONADO Y COSTE HORA</t>
+        </is>
+      </c>
+    </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>HORAS, DIMENSIONADO Y COSTE HORA</t>
-        </is>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Horas contratadas a la semana</t>
+        </is>
+      </c>
+      <c r="B39" s="26">
+        <f>IFERROR(J9,"")</f>
+        <v>100.0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Horas contratadas a la semana</t>
-        </is>
-      </c>
-      <c r="B40" s="26">
-        <f>IFERROR(J9,"")</f>
-        <v>100.0</v>
+          <t>Jornadas completas equivalentes</t>
+        </is>
+      </c>
+      <c r="B40" s="19">
+        <f>IFERROR(C9,"")</f>
+        <v>2.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Jornadas completas equivalentes</t>
-        </is>
-      </c>
-      <c r="B41" s="19">
-        <f>IFERROR(C9,"")</f>
-        <v>2.5</v>
+          <t>Personas con más horas de las que da su jornada</t>
+        </is>
+      </c>
+      <c r="B41" s="26">
+        <f>IFERROR(SUMPRODUCT((J6:J8&gt;C6:C8*'0. Supuestos'!$B$32)*1),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>Tiene que valer cero. Si se pone en rojo, alguien está contratado a media jornada y trabajando más horas de las que cobra: eso no es un ahorro, es una inspección.</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Personas con más horas de las que da su jornada</t>
-        </is>
-      </c>
-      <c r="B42" s="26">
-        <f>IFERROR(SUMPRODUCT((J6:J8&gt;C6:C8*'0. Supuestos'!$B$32)*1),"")</f>
-        <v>0.0</v>
+          <t>Horas anuales de contrato</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="n">
+        <v>1780</v>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>Tiene que valer cero. Si se pone en rojo, alguien está contratado a media jornada y trabajando más horas de las que cobra: eso no es un ahorro, es una inspección.</t>
+          <t>SUPUESTO: 40 h x 52 semanas = 2.080, menos 30 días naturales de vacaciones y los festivos del calendario laboral.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Horas anuales de contrato</t>
-        </is>
-      </c>
-      <c r="B43" s="11" t="n">
-        <v>1780</v>
+          <t>Parte de la jornada a pie de mesa (%)</t>
+        </is>
+      </c>
+      <c r="B43" s="16" t="n">
+        <v>0.85</v>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>SUPUESTO: 40 h x 52 semanas = 2.080, menos 30 días naturales de vacaciones y los festivos del calendario laboral.</t>
+          <t>SUPUESTO. El resto es recepción de mercancía, limpieza, formación y reuniones. Si lo pones al 100 % estarás repartiendo el coste de personal entre horas que no existen.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Parte de la jornada a pie de mesa (%)</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="n">
-        <v>0.85</v>
+      <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>COSTE DE UNA HORA DE OBRADOR (€)</t>
+        </is>
+      </c>
+      <c r="B44" s="24">
+        <f>IFERROR(SUMPRODUCT((K6:K8="OBRADOR")*I6:I8)/SUMPRODUCT((K6:K8="OBRADOR")*C6:C8*B6:B8)/$B$42/$B$43,"")</f>
+        <v>18.49165895571712</v>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>SUPUESTO. El resto es recepción de mercancía, limpieza, formación y reuniones. Si lo pones al 100 % estarás repartiendo el coste de personal entre horas que no existen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="22" t="inlineStr">
-        <is>
-          <t>COSTE DE UNA HORA DE OBRADOR (€)</t>
-        </is>
-      </c>
-      <c r="B45" s="24">
-        <f>IFERROR(SUMPRODUCT((K6:K8="OBRADOR")*I6:I8)/SUMPRODUCT((K6:K8="OBRADOR")*C6:C8*B6:B8)/$B$43/$B$44,"")</f>
-        <v>18.49165895571712</v>
-      </c>
-      <c r="L45" s="5" t="inlineStr">
-        <is>
           <t>Coste empresa de las personas del ÁREA OBRADOR dividido entre sus horas PRODUCTIVAS. No es el bruto ni el bruto con Seguridad Social: es lo que de verdad cuesta un minuto de templado, y es el número que usan el escandallo del libro 4 y la hoja de talleres para saber lo que cuesta un docente.</t>
         </is>
       </c>
     </row>
-    <row r="46"/>
-    <row r="47" ht="58" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="45"/>
+    <row r="46" ht="58" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>El refuerzo de las campañas NO está en este cuadro: la estacionalidad manda horas extra en Navidad, en San Valentín y en comuniones, y eso se dimensiona y se cuesta en el libro «campanas-y-valle-del-ano». Aquí está la plantilla ESTABLE, que es la que entra en los costes fijos del P&amp;L. Y una nota de método: los tres nombres de perfil son los de las hojas del kit de tareas -Encargado, Chocolatero y Dependiente-, no «maestro chocolatero» ni «bombonero», que son etiquetas de fuentes salariales y no puestos de esta casa.</t>
         </is>
@@ -8198,11 +8169,12 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="33">
+  <mergeCells count="30">
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="E34:K34"/>
     <mergeCell ref="B36:D36"/>
+    <mergeCell ref="A46:L46"/>
     <mergeCell ref="I13:L13"/>
     <mergeCell ref="E36:K36"/>
     <mergeCell ref="G15:H15"/>
@@ -8210,37 +8182,33 @@
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="I15:L15"/>
     <mergeCell ref="I17:L17"/>
-    <mergeCell ref="E37:K37"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="I14:L14"/>
-    <mergeCell ref="B18:D18"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="E33:K33"/>
     <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B32:D32"/>
     <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="A47:L47"/>
     <mergeCell ref="A3:L3"/>
+    <mergeCell ref="E32:K32"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="E35:K35"/>
     <mergeCell ref="B33:D33"/>
-    <mergeCell ref="I18:L18"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="I12:L12"/>
     <mergeCell ref="B12:D12"/>
   </mergeCells>
-  <conditionalFormatting sqref="B42">
+  <conditionalFormatting sqref="B41">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
-      <formula>=AND(ISNUMBER($B$42),$B$42&gt;0)</formula>
+      <formula>=AND(ISNUMBER($B$41),$B$41&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="D6 D7 D8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Elige un grupo del convenio" error="Escribe uno de los grupos de la tabla del convenio de abajo." type="list">
-      <formula1>'Personal'!$A$13:$A$18</formula1>
+      <formula1>'Personal'!$A$13:$A$17</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>

--- a/astro-site/public/dl/guia-chocolateria-obrador/plan-financiero-3-anos-chocolateria.xlsx
+++ b/astro-site/public/dl/guia-chocolateria-obrador/plan-financiero-3-anos-chocolateria.xlsx
@@ -7660,7 +7660,7 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>ADMINISTRACION</t>
+          <t>ADMINISTRACIÓN</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>OBRADOR / TIENDA / ADMINISTRACION</t>
+          <t>OBRADOR / TIENDA / ADMINISTRACIÓN</t>
         </is>
       </c>
       <c r="I14" s="9" t="inlineStr">

--- a/astro-site/public/dl/guia-chocolateria-obrador/plan-financiero-3-anos-chocolateria.xlsx
+++ b/astro-site/public/dl/guia-chocolateria-obrador/plan-financiero-3-anos-chocolateria.xlsx
@@ -3870,7 +3870,7 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas. Con un negocio tan estacional como éste, la holgura no es un lujo: es lo que te deja llegar a octubre.</t>
+          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto. Con un negocio tan estacional como éste, la holgura no es un lujo: es lo que te deja llegar a octubre.</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de no poder pagar los fijos y la cuota. El mínimo exigible está en «0. Supuestos».</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en «0. Supuestos».</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/guia-chocolateria-obrador/plan-financiero-3-anos-chocolateria.xlsx
+++ b/astro-site/public/dl/guia-chocolateria-obrador/plan-financiero-3-anos-chocolateria.xlsx
@@ -3870,7 +3870,7 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto. Con un negocio tan estacional como éste, la holgura no es un lujo: es lo que te deja llegar a octubre.</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto. Con un negocio tan estacional como éste, la holgura no es un lujo: es lo que te deja llegar a octubre.</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/guia-chocolateria-obrador/plan-financiero-3-anos-chocolateria.xlsx
+++ b/astro-site/public/dl/guia-chocolateria-obrador/plan-financiero-3-anos-chocolateria.xlsx
@@ -3870,7 +3870,7 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas. Con un negocio tan estacional como éste, la holgura no es un lujo: es lo que te deja llegar a octubre.</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto. Con un negocio tan estacional como éste, la holgura no es un lujo: es lo que te deja llegar a octubre.</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de no poder pagar los fijos y la cuota. El mínimo exigible está en «0. Supuestos».</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en «0. Supuestos».</t>
         </is>
       </c>
     </row>
